--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/28,09,26 Останкино КИ и ЗПФ/машина САП 04,10 БарановКарлова_Малахутин_ПРС_Донецк КИ/Заказ ЛП опт Малахутин 04,10,26.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/28,09,26 Останкино КИ и ЗПФ/машина САП 04,10 БарановКарлова_Малахутин_ПРС_Донецк КИ/Заказ ЛП опт Малахутин 04,10,26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\30,09 Малахутин ЛП\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\28,09,26 Останкино КИ и ЗПФ\машина САП 04,10 БарановКарлова_Малахутин_ПРС_Донецк КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D4F2E9-A5D4-4630-ADAB-A8C820A6DD5D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51192B7-0C92-4F87-8A38-1AC5D51E77F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6441,7 +6441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BO1710"/>
@@ -6667,7 +6667,7 @@
       <c r="BN9" s="113"/>
       <c r="BO9" s="113"/>
     </row>
-    <row r="10" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
       <c r="B10" s="43" t="s">
         <v>18</v>
@@ -6681,7 +6681,7 @@
       <c r="I10" s="43"/>
       <c r="J10" s="44"/>
     </row>
-    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="57">
         <v>4561</v>
       </c>
@@ -6767,7 +6767,7 @@
       <c r="BN11" s="114"/>
       <c r="BO11" s="114"/>
     </row>
-    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="146">
         <v>7536</v>
       </c>
@@ -6853,7 +6853,7 @@
       <c r="BN12" s="114"/>
       <c r="BO12" s="114"/>
     </row>
-    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" s="57">
         <v>5851</v>
       </c>
@@ -7251,7 +7251,7 @@
       <c r="J18" s="29"/>
       <c r="L18" s="115"/>
     </row>
-    <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="57">
         <v>6861</v>
       </c>
@@ -7281,7 +7281,7 @@
       <c r="J19" s="29"/>
       <c r="L19" s="115"/>
     </row>
-    <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="57">
         <v>6862</v>
       </c>
@@ -7311,7 +7311,7 @@
       <c r="J20" s="29"/>
       <c r="L20" s="115"/>
     </row>
-    <row r="21" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="146">
         <v>7539</v>
       </c>
@@ -7341,7 +7341,7 @@
       <c r="J21" s="60"/>
       <c r="L21" s="115"/>
     </row>
-    <row r="22" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="57">
         <v>7334</v>
       </c>
@@ -7371,7 +7371,7 @@
       <c r="J22" s="29"/>
       <c r="L22" s="115"/>
     </row>
-    <row r="23" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="57">
         <v>6325</v>
       </c>
@@ -7401,7 +7401,7 @@
       <c r="J23" s="29"/>
       <c r="L23" s="115"/>
     </row>
-    <row r="24" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="57">
         <v>8014</v>
       </c>
@@ -7487,7 +7487,7 @@
       <c r="BN24" s="115"/>
       <c r="BO24" s="115"/>
     </row>
-    <row r="25" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="146">
         <v>7632</v>
       </c>
@@ -7661,7 +7661,7 @@
       <c r="BN26" s="115"/>
       <c r="BO26" s="115"/>
     </row>
-    <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="138">
         <v>6340</v>
       </c>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="L27" s="115"/>
     </row>
-    <row r="28" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="138">
         <v>6341</v>
       </c>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="L28" s="115"/>
     </row>
-    <row r="29" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="57">
         <v>6333</v>
       </c>
@@ -7787,7 +7787,7 @@
       <c r="J30" s="60"/>
       <c r="L30" s="115"/>
     </row>
-    <row r="31" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="57">
         <v>7343</v>
       </c>
@@ -7905,7 +7905,7 @@
       <c r="BN32" s="115"/>
       <c r="BO32" s="115"/>
     </row>
-    <row r="33" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="57">
         <v>7231</v>
       </c>
@@ -7991,7 +7991,7 @@
       <c r="BN33" s="115"/>
       <c r="BO33" s="115"/>
     </row>
-    <row r="34" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="149">
         <v>7514</v>
       </c>
@@ -8079,7 +8079,7 @@
       <c r="BN34" s="115"/>
       <c r="BO34" s="115"/>
     </row>
-    <row r="35" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="149">
         <v>7518</v>
       </c>
@@ -8167,7 +8167,7 @@
       <c r="BN35" s="115"/>
       <c r="BO35" s="115"/>
     </row>
-    <row r="36" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="48" t="s">
         <v>104</v>
       </c>
@@ -8184,7 +8184,7 @@
       <c r="J36" s="44"/>
       <c r="L36" s="115"/>
     </row>
-    <row r="37" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A37" s="57">
         <v>6767</v>
       </c>
@@ -8270,7 +8270,7 @@
       <c r="BN37" s="115"/>
       <c r="BO37" s="115"/>
     </row>
-    <row r="38" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="57">
         <v>6761</v>
       </c>
@@ -8356,7 +8356,7 @@
       <c r="BN38" s="115"/>
       <c r="BO38" s="115"/>
     </row>
-    <row r="39" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="57">
         <v>6764</v>
       </c>
@@ -8442,7 +8442,7 @@
       <c r="BN39" s="115"/>
       <c r="BO39" s="115"/>
     </row>
-    <row r="40" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="57">
         <v>6254</v>
       </c>
@@ -8528,7 +8528,7 @@
       <c r="BN40" s="115"/>
       <c r="BO40" s="115"/>
     </row>
-    <row r="41" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="57">
         <v>7075</v>
       </c>
@@ -8614,7 +8614,7 @@
       <c r="BN41" s="115"/>
       <c r="BO41" s="115"/>
     </row>
-    <row r="42" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="57">
         <v>7083</v>
       </c>
@@ -8788,7 +8788,7 @@
       <c r="BN43" s="115"/>
       <c r="BO43" s="115"/>
     </row>
-    <row r="44" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="57">
         <v>7070</v>
       </c>
@@ -8874,7 +8874,7 @@
       <c r="BN44" s="115"/>
       <c r="BO44" s="115"/>
     </row>
-    <row r="45" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="57">
         <v>7076</v>
       </c>
@@ -8960,7 +8960,7 @@
       <c r="BN45" s="115"/>
       <c r="BO45" s="115"/>
     </row>
-    <row r="46" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="57">
         <v>7271</v>
       </c>
@@ -9134,7 +9134,7 @@
       <c r="BN47" s="115"/>
       <c r="BO47" s="115"/>
     </row>
-    <row r="48" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="57">
         <v>6661</v>
       </c>
@@ -9220,7 +9220,7 @@
       <c r="BN48" s="115"/>
       <c r="BO48" s="115"/>
     </row>
-    <row r="49" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="57">
         <v>6759</v>
       </c>
@@ -9306,7 +9306,7 @@
       <c r="BN49" s="115"/>
       <c r="BO49" s="115"/>
     </row>
-    <row r="50" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="57">
         <v>6762</v>
       </c>
@@ -9392,7 +9392,7 @@
       <c r="BN50" s="115"/>
       <c r="BO50" s="115"/>
     </row>
-    <row r="51" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="57">
         <v>6765</v>
       </c>
@@ -9478,7 +9478,7 @@
       <c r="BN51" s="115"/>
       <c r="BO51" s="115"/>
     </row>
-    <row r="52" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="57">
         <v>7074</v>
       </c>
@@ -9652,7 +9652,7 @@
       <c r="BN53" s="115"/>
       <c r="BO53" s="115"/>
     </row>
-    <row r="54" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="57">
         <v>5819</v>
       </c>
@@ -9738,7 +9738,7 @@
       <c r="BN54" s="115"/>
       <c r="BO54" s="115"/>
     </row>
-    <row r="55" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="57">
         <v>6475</v>
       </c>
@@ -9824,7 +9824,7 @@
       <c r="BN55" s="115"/>
       <c r="BO55" s="115"/>
     </row>
-    <row r="56" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="138">
         <v>7284</v>
       </c>
@@ -10000,7 +10000,7 @@
       <c r="BN57" s="115"/>
       <c r="BO57" s="115"/>
     </row>
-    <row r="58" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="57">
         <v>7601</v>
       </c>
@@ -10086,7 +10086,7 @@
       <c r="BN58" s="115"/>
       <c r="BO58" s="115"/>
     </row>
-    <row r="59" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="138">
         <v>7371</v>
       </c>
@@ -10174,7 +10174,7 @@
       <c r="BN59" s="115"/>
       <c r="BO59" s="115"/>
     </row>
-    <row r="60" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="57">
         <v>6837</v>
       </c>
@@ -10260,7 +10260,7 @@
       <c r="BN60" s="115"/>
       <c r="BO60" s="115"/>
     </row>
-    <row r="61" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="57">
         <v>7080</v>
       </c>
@@ -10290,7 +10290,7 @@
       <c r="J61" s="29"/>
       <c r="L61" s="115"/>
     </row>
-    <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="57">
         <v>6724</v>
       </c>
@@ -10320,7 +10320,7 @@
       <c r="J62" s="29"/>
       <c r="L62" s="115"/>
     </row>
-    <row r="63" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="57">
         <v>7066</v>
       </c>
@@ -10350,7 +10350,7 @@
       <c r="J63" s="29"/>
       <c r="L63" s="115"/>
     </row>
-    <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="138">
         <v>6713</v>
       </c>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="L64" s="115"/>
     </row>
-    <row r="65" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="57">
         <v>7490</v>
       </c>
@@ -10446,7 +10446,7 @@
       <c r="J66" s="29"/>
       <c r="L66" s="115"/>
     </row>
-    <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="57">
         <v>6602</v>
       </c>
@@ -10476,7 +10476,7 @@
       <c r="J67" s="29"/>
       <c r="L67" s="115"/>
     </row>
-    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="146">
         <v>7040</v>
       </c>
@@ -10506,7 +10506,7 @@
       <c r="J68" s="60"/>
       <c r="L68" s="115"/>
     </row>
-    <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="138">
         <v>7521</v>
       </c>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="L69" s="115"/>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="57">
         <v>7073</v>
       </c>
@@ -10568,7 +10568,7 @@
       <c r="J70" s="29"/>
       <c r="L70" s="115"/>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="57">
         <v>7276</v>
       </c>
@@ -10598,7 +10598,7 @@
       <c r="J71" s="29"/>
       <c r="L71" s="115"/>
     </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="57">
         <v>6616</v>
       </c>
@@ -10628,7 +10628,7 @@
       <c r="J72" s="29"/>
       <c r="L72" s="115"/>
     </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="57">
         <v>7044</v>
       </c>
@@ -10658,7 +10658,7 @@
       <c r="J73" s="29"/>
       <c r="L73" s="115"/>
     </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="138">
         <v>7385</v>
       </c>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="L74" s="115"/>
     </row>
-    <row r="75" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="138">
         <v>7460</v>
       </c>
@@ -10722,7 +10722,7 @@
       </c>
       <c r="L75" s="115"/>
     </row>
-    <row r="76" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="48" t="s">
         <v>104</v>
       </c>
@@ -10739,7 +10739,7 @@
       <c r="J76" s="44"/>
       <c r="L76" s="115"/>
     </row>
-    <row r="77" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A77" s="57">
         <v>6527</v>
       </c>
@@ -10801,7 +10801,7 @@
       <c r="J78" s="29"/>
       <c r="L78" s="115"/>
     </row>
-    <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="57">
         <v>6549</v>
       </c>
@@ -10831,7 +10831,7 @@
       <c r="J79" s="29"/>
       <c r="L79" s="115"/>
     </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="57">
         <v>7001</v>
       </c>
@@ -10893,7 +10893,7 @@
       <c r="J81" s="29"/>
       <c r="L81" s="115"/>
     </row>
-    <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="57">
         <v>7059</v>
       </c>
@@ -10923,7 +10923,7 @@
       <c r="J82" s="29"/>
       <c r="L82" s="115"/>
     </row>
-    <row r="83" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="57">
         <v>6609</v>
       </c>
@@ -10955,7 +10955,7 @@
       <c r="J83" s="29"/>
       <c r="L83" s="115"/>
     </row>
-    <row r="84" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="48" t="s">
         <v>104</v>
       </c>
@@ -10972,7 +10972,7 @@
       <c r="J84" s="44"/>
       <c r="L84" s="115"/>
     </row>
-    <row r="85" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A85" s="146">
         <v>7564</v>
       </c>
@@ -11002,7 +11002,7 @@
       <c r="J85" s="60"/>
       <c r="L85" s="115"/>
     </row>
-    <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="57">
         <v>7133</v>
       </c>
@@ -11032,7 +11032,7 @@
       <c r="J86" s="60"/>
       <c r="L86" s="115"/>
     </row>
-    <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="57">
         <v>6946</v>
       </c>
@@ -11062,7 +11062,7 @@
       <c r="J87" s="29"/>
       <c r="L87" s="115"/>
     </row>
-    <row r="88" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="57">
         <v>7132</v>
       </c>
@@ -11252,7 +11252,7 @@
       <c r="J93" s="60"/>
       <c r="L93" s="115"/>
     </row>
-    <row r="94" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="138">
         <v>7489</v>
       </c>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="L94" s="115"/>
     </row>
-    <row r="95" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="57">
         <v>6807</v>
       </c>
@@ -11314,7 +11314,7 @@
       <c r="J95" s="29"/>
       <c r="L95" s="115"/>
     </row>
-    <row r="96" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="57">
         <v>6787</v>
       </c>
@@ -11408,7 +11408,7 @@
       <c r="J98" s="29"/>
       <c r="L98" s="115"/>
     </row>
-    <row r="99" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="57">
         <v>7233</v>
       </c>
@@ -11470,7 +11470,7 @@
       <c r="J100" s="50"/>
       <c r="L100" s="115"/>
     </row>
-    <row r="101" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="57">
         <v>7177</v>
       </c>
@@ -11532,7 +11532,7 @@
       <c r="J102" s="50"/>
       <c r="L102" s="115"/>
     </row>
-    <row r="103" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="149">
         <v>7156</v>
       </c>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="L103" s="115"/>
     </row>
-    <row r="104" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="149">
         <v>7710</v>
       </c>
@@ -11596,7 +11596,7 @@
       </c>
       <c r="L104" s="115"/>
     </row>
-    <row r="105" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="149">
         <v>7562</v>
       </c>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="L105" s="115"/>
     </row>
-    <row r="106" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="149">
         <v>7516</v>
       </c>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="L106" s="115"/>
     </row>
-    <row r="107" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="149">
         <v>7513</v>
       </c>
@@ -11724,7 +11724,7 @@
       <c r="J108" s="50"/>
       <c r="L108" s="115"/>
     </row>
-    <row r="109" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="57">
         <v>7238</v>
       </c>
@@ -11754,7 +11754,7 @@
       <c r="J109" s="50"/>
       <c r="L109" s="115"/>
     </row>
-    <row r="110" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="138">
         <v>7237</v>
       </c>
@@ -11818,7 +11818,7 @@
       <c r="J111" s="50"/>
       <c r="L111" s="115"/>
     </row>
-    <row r="112" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="138">
         <v>7332</v>
       </c>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="L112" s="115"/>
     </row>
-    <row r="113" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="138">
         <v>7333</v>
       </c>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="L113" s="115"/>
     </row>
-    <row r="114" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="146">
         <v>7608</v>
       </c>
@@ -11912,7 +11912,7 @@
       <c r="J114" s="60"/>
       <c r="L114" s="115"/>
     </row>
-    <row r="115" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:67" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A115" s="138">
         <v>7610</v>
       </c>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="L115" s="115"/>
     </row>
-    <row r="116" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="48" t="s">
         <v>104</v>
       </c>
@@ -12017,7 +12017,7 @@
       <c r="BN116" s="115"/>
       <c r="BO116" s="115"/>
     </row>
-    <row r="117" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A117" s="57">
         <v>614</v>
       </c>
@@ -12103,7 +12103,7 @@
       <c r="BN117" s="115"/>
       <c r="BO117" s="115"/>
     </row>
-    <row r="118" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="57">
         <v>3287</v>
       </c>
@@ -12189,7 +12189,7 @@
       <c r="BN118" s="115"/>
       <c r="BO118" s="115"/>
     </row>
-    <row r="119" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="171">
         <v>5708</v>
       </c>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="L119" s="115"/>
     </row>
-    <row r="120" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="174">
         <v>7700</v>
       </c>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="L120" s="115"/>
     </row>
-    <row r="121" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="57">
         <v>4117</v>
       </c>
@@ -12283,7 +12283,7 @@
       <c r="J121" s="29"/>
       <c r="L121" s="115"/>
     </row>
-    <row r="122" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="57">
         <v>7316</v>
       </c>
@@ -12313,7 +12313,7 @@
       <c r="J122" s="29"/>
       <c r="L122" s="115"/>
     </row>
-    <row r="123" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="57">
         <v>7317</v>
       </c>
@@ -12343,7 +12343,7 @@
       <c r="J123" s="29"/>
       <c r="L123" s="115"/>
     </row>
-    <row r="124" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="57">
         <v>7143</v>
       </c>
@@ -12373,7 +12373,7 @@
       <c r="J124" s="29"/>
       <c r="L124" s="115"/>
     </row>
-    <row r="125" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="171">
         <v>7147</v>
       </c>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="L125" s="115"/>
     </row>
-    <row r="126" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="57">
         <v>7456</v>
       </c>
@@ -12435,7 +12435,7 @@
       <c r="J126" s="29"/>
       <c r="L126" s="115"/>
     </row>
-    <row r="127" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="57">
         <v>7318</v>
       </c>
@@ -12497,7 +12497,7 @@
       <c r="J128" s="29"/>
       <c r="L128" s="115"/>
     </row>
-    <row r="129" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="57">
         <v>7364</v>
       </c>
@@ -12527,7 +12527,7 @@
       <c r="J129" s="29"/>
       <c r="L129" s="115"/>
     </row>
-    <row r="130" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="57">
         <v>7383</v>
       </c>
@@ -12557,7 +12557,7 @@
       <c r="J130" s="29"/>
       <c r="L130" s="115"/>
     </row>
-    <row r="131" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="57">
         <v>6967</v>
       </c>
@@ -12587,7 +12587,7 @@
       <c r="J131" s="29"/>
       <c r="L131" s="115"/>
     </row>
-    <row r="132" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="57">
         <v>4993</v>
       </c>
@@ -12617,7 +12617,7 @@
       <c r="J132" s="29"/>
       <c r="L132" s="115"/>
     </row>
-    <row r="133" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="57">
         <v>6937</v>
       </c>
@@ -12711,7 +12711,7 @@
       <c r="J135" s="29"/>
       <c r="L135" s="115"/>
     </row>
-    <row r="136" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="57">
         <v>6832</v>
       </c>
@@ -12741,7 +12741,7 @@
       <c r="J136" s="29"/>
       <c r="L136" s="115"/>
     </row>
-    <row r="137" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="57">
         <v>7299</v>
       </c>
@@ -12771,7 +12771,7 @@
       <c r="J137" s="29"/>
       <c r="L137" s="115"/>
     </row>
-    <row r="138" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="57">
         <v>7386</v>
       </c>
@@ -12801,7 +12801,7 @@
       <c r="J138" s="29"/>
       <c r="L138" s="115"/>
     </row>
-    <row r="139" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="57">
         <v>5679</v>
       </c>
@@ -12959,7 +12959,7 @@
       <c r="J143" s="29"/>
       <c r="L143" s="115"/>
     </row>
-    <row r="144" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="57">
         <v>6222</v>
       </c>
@@ -12989,7 +12989,7 @@
       <c r="J144" s="29"/>
       <c r="L144" s="115"/>
     </row>
-    <row r="145" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="138">
         <v>6834</v>
       </c>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="L145" s="115"/>
     </row>
-    <row r="146" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="138">
         <v>6965</v>
       </c>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="L146" s="115"/>
     </row>
-    <row r="147" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="138">
         <v>6557</v>
       </c>
@@ -13085,7 +13085,7 @@
       </c>
       <c r="L147" s="115"/>
     </row>
-    <row r="148" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A148" s="146">
         <v>7626</v>
       </c>
@@ -13115,7 +13115,7 @@
       <c r="J148" s="60"/>
       <c r="L148" s="115"/>
     </row>
-    <row r="149" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="48" t="s">
         <v>104</v>
       </c>
@@ -13132,7 +13132,7 @@
       <c r="J149" s="44"/>
       <c r="L149" s="115"/>
     </row>
-    <row r="150" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:67" ht="16.149999999999999" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A150" s="171">
         <v>6470</v>
       </c>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="L150" s="115"/>
     </row>
-    <row r="151" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:67" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="174">
         <v>7726</v>
       </c>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="L151" s="115"/>
     </row>
-    <row r="152" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="179">
         <v>6495</v>
       </c>
@@ -13284,7 +13284,7 @@
       <c r="BN152" s="115"/>
       <c r="BO152" s="115"/>
     </row>
-    <row r="153" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="174">
         <v>7725</v>
       </c>
@@ -13372,7 +13372,7 @@
       <c r="BN153" s="115"/>
       <c r="BO153" s="115"/>
     </row>
-    <row r="154" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="57">
         <v>5452</v>
       </c>
@@ -13458,7 +13458,7 @@
       <c r="BN154" s="115"/>
       <c r="BO154" s="115"/>
     </row>
-    <row r="155" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="57">
         <v>6866</v>
       </c>
@@ -13544,7 +13544,7 @@
       <c r="BN155" s="115"/>
       <c r="BO155" s="115"/>
     </row>
-    <row r="156" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="57">
         <v>6025</v>
       </c>
@@ -13630,7 +13630,7 @@
       <c r="BN156" s="115"/>
       <c r="BO156" s="115"/>
     </row>
-    <row r="157" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="57">
         <v>4584</v>
       </c>
@@ -13716,7 +13716,7 @@
       <c r="BN157" s="115"/>
       <c r="BO157" s="115"/>
     </row>
-    <row r="158" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="57">
         <v>3215</v>
       </c>
@@ -13890,7 +13890,7 @@
       <c r="BN159" s="115"/>
       <c r="BO159" s="115"/>
     </row>
-    <row r="160" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:67" s="61" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="57">
         <v>7377</v>
       </c>
@@ -13976,7 +13976,7 @@
       <c r="BN160" s="115"/>
       <c r="BO160" s="115"/>
     </row>
-    <row r="161" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="179">
         <v>6925</v>
       </c>
@@ -14064,7 +14064,7 @@
       <c r="BN161" s="115"/>
       <c r="BO161" s="115"/>
     </row>
-    <row r="162" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="183">
         <v>7723</v>
       </c>
@@ -14152,7 +14152,7 @@
       <c r="BN162" s="115"/>
       <c r="BO162" s="115"/>
     </row>
-    <row r="163" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="171">
         <v>7647</v>
       </c>
@@ -14240,7 +14240,7 @@
       <c r="BN163" s="115"/>
       <c r="BO163" s="115"/>
     </row>
-    <row r="164" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="174">
         <v>7730</v>
       </c>
@@ -14328,7 +14328,7 @@
       <c r="BN164" s="115"/>
       <c r="BO164" s="115"/>
     </row>
-    <row r="165" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="171">
         <v>7651</v>
       </c>
@@ -14416,7 +14416,7 @@
       <c r="BN165" s="115"/>
       <c r="BO165" s="115"/>
     </row>
-    <row r="166" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A166" s="174">
         <v>7731</v>
       </c>
@@ -14504,7 +14504,7 @@
       <c r="BN166" s="115"/>
       <c r="BO166" s="115"/>
     </row>
-    <row r="167" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="48" t="s">
         <v>104</v>
       </c>
@@ -14577,7 +14577,7 @@
       <c r="BN167" s="115"/>
       <c r="BO167" s="115"/>
     </row>
-    <row r="168" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:67" s="61" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A168" s="146">
         <v>7485</v>
       </c>
@@ -14663,7 +14663,7 @@
       <c r="BN168" s="115"/>
       <c r="BO168" s="115"/>
     </row>
-    <row r="169" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="48" t="s">
         <v>104</v>
       </c>
@@ -14680,7 +14680,7 @@
       <c r="J169" s="44"/>
       <c r="L169" s="115"/>
     </row>
-    <row r="170" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A170" s="57">
         <v>6620</v>
       </c>
@@ -14710,7 +14710,7 @@
       <c r="J170" s="29"/>
       <c r="L170" s="115"/>
     </row>
-    <row r="171" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="57">
         <v>7187</v>
       </c>
@@ -14740,7 +14740,7 @@
       <c r="J171" s="29"/>
       <c r="L171" s="115"/>
     </row>
-    <row r="172" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="146">
         <v>6008</v>
       </c>
@@ -14770,7 +14770,7 @@
       <c r="J172" s="60"/>
       <c r="L172" s="115"/>
     </row>
-    <row r="173" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="57">
         <v>7090</v>
       </c>
@@ -14864,7 +14864,7 @@
       <c r="J175" s="29"/>
       <c r="L175" s="115"/>
     </row>
-    <row r="176" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="149">
         <v>6929</v>
       </c>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="L176" s="115"/>
     </row>
-    <row r="177" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="57">
         <v>7092</v>
       </c>
@@ -14926,7 +14926,7 @@
       <c r="J177" s="29"/>
       <c r="L177" s="115"/>
     </row>
-    <row r="178" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="138">
         <v>6448</v>
       </c>
@@ -15086,7 +15086,7 @@
       <c r="J182" s="60"/>
       <c r="L182" s="115"/>
     </row>
-    <row r="183" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="48" t="s">
         <v>104</v>
       </c>
@@ -15103,7 +15103,7 @@
       <c r="J183" s="44"/>
       <c r="L183" s="115"/>
     </row>
-    <row r="184" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A184" s="149">
         <v>7344</v>
       </c>
@@ -15131,7 +15131,7 @@
       </c>
       <c r="L184" s="115"/>
     </row>
-    <row r="185" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="149">
         <v>7345</v>
       </c>
@@ -30423,7 +30423,13 @@
       <c r="J1710" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:J186" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J186" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
